--- a/field_trial_data_clean_seed.xlsx
+++ b/field_trial_data_clean_seed.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sites" sheetId="1" r:id="Ra71845d8393b444b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Builds" sheetId="2" r:id="Re1d76b09b2274bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traps" sheetId="3" r:id="Rd30718c968104f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visits" sheetId="4" r:id="Re0d960de8b2a4add"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R8569ea3e6cdb471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Windows" sheetId="6" r:id="Re4b19e43c98346e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Followups" sheetId="7" r:id="Rf78c15cfc07f4e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="8" r:id="R45d527f6ee884104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="9" r:id="R1af8f1560d4c4419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sites" sheetId="1" r:id="R0b44e84c812d4663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Builds" sheetId="2" r:id="Rf481e7c8c6954f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traps" sheetId="3" r:id="R916f195167694601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visits" sheetId="4" r:id="Rba19d7de6f064ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R565a4a40ec5a4b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Windows" sheetId="6" r:id="R6051e95f50c7451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Followups" sheetId="7" r:id="R29e76427df70482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="8" r:id="Rbd516d0f7da14b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="9" r:id="R3192dd3bd2a34389"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -688,7 +688,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Route point 1</x:v>
+        <x:v>Trap 1</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
         <x:v>CAM-HUT-001</x:v>
@@ -762,7 +762,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="7" t="str">
-        <x:v>Route point 2</x:v>
+        <x:v>Trap 2</x:v>
       </x:c>
       <x:c r="G3" s="7"/>
       <x:c r="H3" s="7" t="str">
@@ -834,7 +834,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="7" t="str">
-        <x:v>Route point 3</x:v>
+        <x:v>Trap 3</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="str">
@@ -906,7 +906,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>Route point 4</x:v>
+        <x:v>Trap 4</x:v>
       </x:c>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7" t="str">
@@ -978,7 +978,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>Route point 1</x:v>
+        <x:v>Trap 1</x:v>
       </x:c>
       <x:c r="G6" s="7" t="str">
         <x:v>CAM-NAE-001</x:v>
@@ -1052,7 +1052,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
-        <x:v>Route point 2</x:v>
+        <x:v>Trap 2</x:v>
       </x:c>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="str">
@@ -1124,7 +1124,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>Route point 3</x:v>
+        <x:v>Trap 3</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="str">
@@ -1196,7 +1196,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>Route point 4</x:v>
+        <x:v>Trap 4</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="str">
@@ -1268,7 +1268,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>Route point 1</x:v>
+        <x:v>Trap 1</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>CAM-TAW-001</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>Route point 2</x:v>
+        <x:v>Trap 2</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="str">
@@ -1414,7 +1414,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
-        <x:v>Route point 3</x:v>
+        <x:v>Trap 3</x:v>
       </x:c>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7" t="str">
@@ -1486,7 +1486,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>Route point 4</x:v>
+        <x:v>Trap 4</x:v>
       </x:c>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7" t="str">
@@ -1558,7 +1558,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>Route point 5</x:v>
+        <x:v>Trap 5</x:v>
       </x:c>
       <x:c r="G14" s="7"/>
       <x:c r="H14" s="7" t="str">
@@ -1630,7 +1630,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>Route point 5</x:v>
+        <x:v>Trap 5</x:v>
       </x:c>
       <x:c r="G15" s="7"/>
       <x:c r="H15" s="7" t="str">
@@ -1702,7 +1702,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>Route point 5</x:v>
+        <x:v>Trap 5</x:v>
       </x:c>
       <x:c r="G16" s="7"/>
       <x:c r="H16" s="7" t="str">
